--- a/AAII_Financials/Quarterly/APLT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APLT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
   <si>
     <t>APLT</t>
   </si>
@@ -656,136 +656,139 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43190</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>10000</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
       </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>10700</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,8 +804,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -846,8 +849,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -923,8 +929,11 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1000,8 +1009,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,85 +1041,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>53900</v>
+      </c>
+      <c r="E12" s="3">
         <v>10800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>15900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>13100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>15400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>15000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>17600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>14800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>14400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>19900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>20800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1400</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1199,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1260,8 +1279,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1337,8 +1359,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,100 +1388,104 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E17" s="3">
         <v>15500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>19400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>21500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>28400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>30000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>17700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1900</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-64500</v>
       </c>
       <c r="E18" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-17200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10800</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1472,53 +1501,56 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>-25900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-23700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-28300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-12500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-17700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,23 +1578,24 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-55200</v>
       </c>
       <c r="E20" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="F20" s="3">
         <v>-12400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,27 +1611,27 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1609,37 +1642,40 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-119800</v>
       </c>
       <c r="E21" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-29600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10100</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1700,8 +1736,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1777,85 +1816,91 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-119800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-42400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-29600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-19100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-25900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-23100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-27200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-25800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-24200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-23700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-29800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-28100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-12400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-17600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1931,8 +1976,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2056,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-119800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-42400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-29600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-19100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-25900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-23100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-27200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-28400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-24200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-23700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-29800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-28100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-12400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-17600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-119800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-42400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-29600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-19100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-23100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-27200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-28400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-25800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-24200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-23700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-29800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-28100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-12400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-17600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2296,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2376,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2456,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,23 +2536,26 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>55200</v>
       </c>
       <c r="E32" s="3">
+        <v>26900</v>
+      </c>
+      <c r="F32" s="3">
         <v>12400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2502,27 +2571,27 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2533,99 +2602,105 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-119800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-42400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-29600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-14400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-19100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-23100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-27200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-28400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-25800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-24200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-23700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-29800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-28100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-12400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-17600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-10700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2776,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-119800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-42400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-29600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-14400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-19100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-23100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-27200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-28400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-25800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-24200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-23700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-29800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-28100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-12400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-17600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-10700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43190</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2973,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,71 +3003,72 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E41" s="3">
         <v>37500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>35600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>40400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>55700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>38200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>53900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>70200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>78400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>84100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>57500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>48700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>100900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>92500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>18900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>13100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>41100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>14700</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,13 +3081,16 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -3010,50 +3099,50 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>13900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>12000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>17400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>26900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>38600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>47200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>64000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>39400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>67800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>37600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>61800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>20000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>19900</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3072,8 +3161,11 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3149,8 +3241,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3226,71 +3321,74 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E45" s="3">
         <v>7000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2200</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3303,71 +3401,74 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E46" s="3">
         <v>44500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>42800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>37300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>55500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>76900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>63600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>88400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>116900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>135300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>154400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>102600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>122900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>148500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>163700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>46200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>37000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>46800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16900</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3380,8 +3481,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3457,62 +3561,65 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>400</v>
+      </c>
+      <c r="E48" s="3">
         <v>500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1700</v>
-      </c>
-      <c r="P48" s="3">
-        <v>1800</v>
       </c>
       <c r="Q48" s="3">
         <v>1800</v>
       </c>
       <c r="R48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="S48" s="3">
         <v>1900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2000</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3525,8 +3632,8 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
@@ -3534,8 +3641,11 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3611,8 +3721,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3801,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,13 +3881,16 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
@@ -3821,8 +3940,8 @@
       <c r="T52" s="3">
         <v>200</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
+      <c r="U52" s="3">
+        <v>200</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
@@ -3842,8 +3961,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,71 +4041,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E54" s="3">
         <v>45200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>43600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>38400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>56700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>78200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>65000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>89900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>118500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>137000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>156200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>104500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>124800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>150600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>165900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>48400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>37300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>46800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16900</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,8 +4121,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4153,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,71 +4183,72 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E57" s="3">
         <v>6000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2600</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4131,8 +4261,11 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4208,71 +4341,74 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E59" s="3">
         <v>49500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>27700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>28900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>39500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>43000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3700</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4285,71 +4421,74 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>71200</v>
+      </c>
+      <c r="E60" s="3">
         <v>55500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>47200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>46500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>51700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>23400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>20500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6300</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4362,8 +4501,11 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4439,62 +4581,65 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>800</v>
+      </c>
+      <c r="E62" s="3">
         <v>700</v>
-      </c>
-      <c r="E62" s="3">
-        <v>800</v>
       </c>
       <c r="F62" s="3">
         <v>800</v>
       </c>
       <c r="G62" s="3">
+        <v>800</v>
+      </c>
+      <c r="H62" s="3">
         <v>900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1700</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4507,8 +4652,8 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -4516,8 +4661,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4741,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4821,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,71 +4901,74 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E66" s="3">
         <v>56200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>48000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>34100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>34300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>47100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>23000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>31800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>24500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>21900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6300</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4824,8 +4981,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5013,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5091,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5171,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5067,11 +5234,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>38500</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5084,8 +5251,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,71 +5331,74 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-468600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-430900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-388500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-359000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-348800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-334400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-315300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-289400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-266300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-239200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-210700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-184900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-160700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-137000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-107200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-79100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-66800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-49100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-38400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-30000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5238,8 +5411,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5491,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5571,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,71 +5651,74 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-11000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-4300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-4100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>25800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>42000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>62500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>86700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>112400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>135200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>81900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>102900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>130200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>155800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>32600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>30700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>40000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-27900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5546,8 +5731,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5811,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43190</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-119800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-42400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-29600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-14400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-19100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-23100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-27200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-28400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-25800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-24200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-23700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-29800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-28100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-12400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-17600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-10700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,19 +6008,20 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>0</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
@@ -5831,11 +6029,11 @@
       <c r="H83" s="3">
         <v>0</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -5843,8 +6041,8 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -5888,8 +6086,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6166,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6246,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6326,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6406,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6486,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-55200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-14700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-16500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-15900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-19400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-18400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-24400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-26900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-15700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-25900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-22200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-22800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-18900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-12400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-9100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,8 +6598,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6456,8 +6676,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6756,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,62 +6836,65 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>13900</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>13900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>5000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>5500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>9500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>11800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>8500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>16800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-24700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>28400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-30200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>24000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-41700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6678,8 +6907,8 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -6687,8 +6916,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6948,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6793,8 +7026,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7106,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7186,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,85 +7266,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E100" s="3">
         <v>16600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>29200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>30400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>73500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>134200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>18300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>35400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2900</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>5600</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7178,81 +7426,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E102" s="3">
         <v>1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-23700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>17500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-16300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>26600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-52200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>73700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-28000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>26400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4400</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/APLT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APLT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>APLT</t>
   </si>
@@ -656,142 +656,146 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3">
         <v>10000</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
       <c r="F8" s="3">
         <v>0</v>
       </c>
       <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>10700</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -807,8 +811,8 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -852,8 +856,11 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -932,8 +939,11 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1012,8 +1022,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1042,88 +1055,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E12" s="3">
         <v>53900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>15900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>13100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>15400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>14800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>20800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1400</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1202,8 +1219,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1282,8 +1302,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1362,8 +1385,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1389,106 +1415,110 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E17" s="3">
         <v>74500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>19000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>21500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>30000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>28300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>17700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1900</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-64500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-15500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-17200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10800</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1504,53 +1534,56 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3">
         <v>-25900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-30000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-28300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-12500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-17700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1579,26 +1612,27 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-62900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-55200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-26900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-12400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1614,27 +1648,27 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1645,40 +1679,43 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-119800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-42400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-29600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-10100</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1739,8 +1776,11 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1819,88 +1859,94 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-119800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-42400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-29600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-19100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-25900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-23100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-27200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-28400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-25800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-29800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-28100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-12400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-17600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1979,8 +2025,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2059,168 +2108,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-119800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-42400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-29600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-19100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-23100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-27200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-28400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-24200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-29800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-28100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-12400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-17600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-119800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-42400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-29600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-19100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-23100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-27200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-28400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-24200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-29800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-28100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-12400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-17600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2299,8 +2357,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2379,8 +2440,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2459,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2539,26 +2606,29 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E32" s="3">
         <v>55200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>26900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>12400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2574,27 +2644,27 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -2605,102 +2675,108 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-119800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-42400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-29600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-19100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-23100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-27200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-28400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-24200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-29800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-28100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-12400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-17600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2779,173 +2855,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-119800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-42400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-29600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-19100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-23100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-27200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-28400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-24200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-29800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-28100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-12400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-17600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2974,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3004,74 +3090,75 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E41" s="3">
         <v>49900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>37500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>35600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>22900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>40400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>55700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>38200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>53900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>70200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>78400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>84100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>57500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>48700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>100900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>92500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>18900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>13100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>41100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>14700</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3084,8 +3171,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3093,7 +3183,7 @@
         <v>300</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -3102,50 +3192,50 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>13900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>12000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>17400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>26900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>38600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>47200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>64000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>39400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>67800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>37600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>61800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>20000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>19900</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3164,31 +3254,34 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3244,8 +3337,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3324,74 +3420,77 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E45" s="3">
         <v>4200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2200</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3404,74 +3503,77 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>150900</v>
+      </c>
+      <c r="E46" s="3">
         <v>54400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>44500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>42800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>29100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>37300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>55500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>76900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>63600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>88400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>116900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>135300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>154400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>102600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>122900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>148500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>163700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>46200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>37000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>46800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16900</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3484,8 +3586,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3564,65 +3669,68 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>300</v>
+      </c>
+      <c r="E48" s="3">
         <v>400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1700</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>1800</v>
       </c>
       <c r="R48" s="3">
         <v>1800</v>
       </c>
       <c r="S48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T48" s="3">
         <v>1900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2000</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3635,8 +3743,8 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
@@ -3644,8 +3752,11 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3724,8 +3835,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3804,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3884,16 +4001,19 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
         <v>200</v>
@@ -3943,8 +4063,8 @@
       <c r="U52" s="3">
         <v>200</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
+      <c r="V52" s="3">
+        <v>200</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
@@ -3964,8 +4084,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4044,74 +4167,77 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>151200</v>
+      </c>
+      <c r="E54" s="3">
         <v>54800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>45200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>43600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>38400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>56700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>78200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>65000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>89900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>118500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>137000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>156200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>104500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>124800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>150600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>165900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>48400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>37300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>46800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16900</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4124,8 +4250,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4154,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4184,74 +4314,75 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2600</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4264,8 +4395,11 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4344,74 +4478,77 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>79900</v>
+      </c>
+      <c r="E59" s="3">
         <v>69400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>49500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>42500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>27700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>28900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>39500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>43000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3700</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4424,74 +4561,77 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E60" s="3">
         <v>71200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>55500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>47200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>46500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>51700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>23400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>20500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6300</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4504,8 +4644,11 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4584,65 +4727,68 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
         <v>800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>700</v>
-      </c>
-      <c r="F62" s="3">
-        <v>800</v>
       </c>
       <c r="G62" s="3">
         <v>800</v>
       </c>
       <c r="H62" s="3">
+        <v>800</v>
+      </c>
+      <c r="I62" s="3">
         <v>900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1700</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4655,8 +4801,8 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -4664,8 +4810,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4744,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4824,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4904,74 +5059,77 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E66" s="3">
         <v>72000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>56200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>48000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>34100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>52400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>23000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>31800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>24500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>21900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6300</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,8 +5142,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5014,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5094,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5174,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5237,11 +5405,11 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>38500</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5254,8 +5422,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5334,74 +5505,77 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-552500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-468600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-430900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-388500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-359000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-348800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-334400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-315300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-289400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-266300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-239200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-210700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-184900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-160700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-137000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-107200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-79100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-66800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-49100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-38400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-30000</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5414,8 +5588,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5494,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5574,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5654,74 +5837,77 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E76" s="3">
         <v>-17100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-11000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-4300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-4100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>42000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>62500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>86700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>112400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>135200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>81900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>102900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>130200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>155800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>32600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>30700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>40000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-27900</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5734,8 +5920,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5814,173 +6003,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-119800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-42400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-29600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-19100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-23100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-27200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-28400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-24200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-29800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-28100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-12400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-17600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6009,8 +6207,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6035,8 +6234,8 @@
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -6044,8 +6243,8 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -6089,8 +6288,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6169,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6249,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6329,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6409,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6489,88 +6703,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-55200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-16500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-15900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-19400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-18400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-24400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-26900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-25900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-22200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-22800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-20700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-18900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-12400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-9100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6599,8 +6819,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6679,8 +6900,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6759,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6839,65 +7066,68 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>13900</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>13900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>5000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>5500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>9500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>11800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>8500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>16800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-24700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>28400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-30200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>24000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-41700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6910,8 +7140,8 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -6919,8 +7149,11 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6949,8 +7182,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7029,8 +7263,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7109,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7189,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7269,88 +7512,94 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>115500</v>
+      </c>
+      <c r="E100" s="3">
         <v>74500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>16600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>29200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>30400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>73500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>134200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>18300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>35400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2900</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>5600</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7429,84 +7678,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>96600</v>
+      </c>
+      <c r="E102" s="3">
         <v>33200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-23700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>17500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-16300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>26600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-52200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>73700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-28000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>26400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4400</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/APLT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APLT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
   <si>
     <t>APLT</t>
   </si>
@@ -656,149 +656,153 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10000</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>10700</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -814,8 +818,8 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -859,8 +863,11 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -942,8 +949,11 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1025,8 +1035,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,91 +1069,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E12" s="3">
         <v>12200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>53900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>15900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>17600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>19900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>20800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1400</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1222,8 +1239,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1305,8 +1325,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1388,8 +1411,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,112 +1442,116 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E17" s="3">
         <v>21300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>74500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>24200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>30000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>28300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>17700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1900</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-21100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-64500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-15500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-17200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10800</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1537,53 +1567,56 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3">
         <v>-25900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-23700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-30000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-28300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-12500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-17700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,29 +1646,30 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-62900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-55200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-26900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-12400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1651,27 +1685,27 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>100</v>
+      </c>
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1682,43 +1716,46 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-500</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-83900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-119800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-42400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-29600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-10100</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1779,8 +1816,11 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1862,91 +1902,97 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-83900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-119800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-42400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-29600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-19100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-25900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-23100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-27200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-25800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-23700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-29800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-28100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-12400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-17600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2028,8 +2074,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-83900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-119800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-42400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-29600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-19100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-23100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-27200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-28400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-25800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-23700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-29800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-28100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-12400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-17600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-83900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-119800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-42400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-29600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-19100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-23100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-27200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-28400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-25800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-23700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-29800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-28100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-12400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-17600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2443,8 +2504,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,29 +2676,32 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E32" s="3">
         <v>62900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>55200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>26900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>12400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,27 +2717,27 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2678,105 +2748,111 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>500</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-83900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-119800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-42400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-29600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-19100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-23100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-27200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-28400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-25800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-23700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-29800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-28100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-12400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-17600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-10700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-83900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-119800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-42400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-29600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-19100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-23100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-27200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-28400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-25800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-23700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-29800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-28100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-12400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-17600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-10700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,77 +3177,78 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>122200</v>
+      </c>
+      <c r="E41" s="3">
         <v>146500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>49900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>37500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>35600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>22900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>40400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>55700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>38200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>53900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>70200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>78400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>84100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>57500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>48700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>100900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>92500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>18900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>13100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>41100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>14700</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,8 +3261,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3186,7 +3276,7 @@
         <v>300</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -3195,50 +3285,50 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>13900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>12000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>17400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>26900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>38600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>47200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>64000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>39400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>67800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>37600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>61800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>20000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>19900</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3257,16 +3347,19 @@
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
+      <c r="E43" s="3">
+        <v>300</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -3283,8 +3376,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3340,8 +3433,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3423,77 +3519,80 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E45" s="3">
         <v>3900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2200</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,77 +3605,80 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>127600</v>
+      </c>
+      <c r="E46" s="3">
         <v>150900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>54400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>44500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>42800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>29100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>37300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>55500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>76900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>63600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>88400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>116900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>135300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>154400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>102600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>122900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>148500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>163700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>46200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>37000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>46800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16900</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3589,8 +3691,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3672,68 +3777,71 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>200</v>
+      </c>
+      <c r="E48" s="3">
         <v>300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1700</v>
-      </c>
-      <c r="R48" s="3">
-        <v>1800</v>
       </c>
       <c r="S48" s="3">
         <v>1800</v>
       </c>
       <c r="T48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="U48" s="3">
         <v>1900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2000</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3746,8 +3854,8 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
@@ -3755,8 +3863,11 @@
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3838,8 +3949,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,19 +4121,22 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
         <v>200</v>
@@ -4066,8 +4186,8 @@
       <c r="V52" s="3">
         <v>200</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
+      <c r="W52" s="3">
+        <v>200</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
@@ -4087,8 +4207,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,77 +4293,80 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>127800</v>
+      </c>
+      <c r="E54" s="3">
         <v>151200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>54800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>45200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>43600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>38400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>56700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>78200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>65000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>89900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>118500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>137000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>156200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>104500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>124800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>150600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>165900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>48400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>37300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>46800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>16900</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4253,8 +4379,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,77 +4445,78 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
         <v>4000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2600</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4398,8 +4529,11 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4481,77 +4615,80 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E59" s="3">
         <v>79900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>69400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>49500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>42500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>27700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>28900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>39500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>43000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>20600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3700</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4564,77 +4701,80 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E60" s="3">
         <v>83900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>71200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>55500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>46500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>51700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>23400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>19800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>20500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>18900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>14100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6300</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4647,8 +4787,11 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4730,8 +4873,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4739,59 +4885,59 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
         <v>800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>800</v>
       </c>
       <c r="H62" s="3">
         <v>800</v>
       </c>
       <c r="I62" s="3">
+        <v>800</v>
+      </c>
+      <c r="J62" s="3">
         <v>900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1700</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4804,8 +4950,8 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -4813,8 +4959,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,77 +5217,80 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E66" s="3">
         <v>83900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>72000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>56200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>34300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>47100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>23000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>31800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>24500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>21000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>21900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6300</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5145,8 +5303,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5408,11 +5576,11 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>38500</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5425,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,77 +5679,80 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-549600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-552500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-468600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-430900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-388500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-359000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-348800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-334400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-315300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-289400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-266300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-239200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-210700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-184900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-160700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-137000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-107200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-79100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-66800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-49100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-38400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-30000</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5591,8 +5765,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,77 +6023,80 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E76" s="3">
         <v>67300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-17100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-11000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-4300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-4100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>42000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>62500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>86700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>112400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>135200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>81900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>102900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>130200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>155800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>32600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>30700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>40000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-27900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5923,8 +6109,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-83900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-119800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-42400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-29600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-19100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-23100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-27200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-28400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-25800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-23700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-29800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-28100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-12400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-17600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-10700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,8 +6406,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6237,8 +6436,8 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -6246,8 +6445,8 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -6291,8 +6490,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,91 +6920,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-18900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-55200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-16500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-15900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-18400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-24400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-26900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-25900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-22800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-20700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-15900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-18900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-12400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-9100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,8 +7040,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6903,8 +7124,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,68 +7296,71 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>13900</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>13900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>5000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>5500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>9500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>11800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>8500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>16800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>28400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-30200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>24000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-41700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7143,8 +7373,8 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -7152,8 +7382,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7266,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,91 +7758,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E100" s="3">
         <v>115500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>74500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>16600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>29200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>30400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>73500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>134200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>18300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>35400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2900</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>5600</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7681,87 +7930,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E102" s="3">
         <v>96600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>33200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-23700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>17500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-16300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>26600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-52200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>73700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-28000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>26400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4400</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/APLT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APLT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>APLT</t>
   </si>
@@ -656,132 +656,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -789,23 +793,23 @@
         <v>100</v>
       </c>
       <c r="E8" s="3">
+        <v>100</v>
+      </c>
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
-        <v>10000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>10700</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -821,8 +825,8 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -866,31 +870,34 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>12200</v>
+      </c>
+      <c r="G9" s="3">
+        <v>53900</v>
+      </c>
+      <c r="H9" s="3">
+        <v>10800</v>
+      </c>
+      <c r="I9" s="3">
+        <v>11900</v>
+      </c>
+      <c r="J9" s="3">
+        <v>15900</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -952,31 +959,34 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-5300</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -1038,8 +1048,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1070,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E12" s="3">
         <v>10000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12200</v>
       </c>
-      <c r="F12" s="3">
-        <v>53900</v>
-      </c>
       <c r="G12" s="3">
+        <v>-38600</v>
+      </c>
+      <c r="H12" s="3">
         <v>10800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>15900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>14400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>19900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>20800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>6900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1400</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1253,11 +1273,11 @@
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1265,8 +1285,8 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1328,8 +1348,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1414,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,117 +1469,121 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E17" s="3">
         <v>20600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21300</v>
       </c>
-      <c r="F17" s="3">
-        <v>74500</v>
-      </c>
       <c r="G17" s="3">
+        <v>20300</v>
+      </c>
+      <c r="H17" s="3">
         <v>15500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>21500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>28400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>30000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>28300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>17700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1900</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-20500</v>
+        <v>-29700</v>
       </c>
       <c r="E18" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-21100</v>
       </c>
-      <c r="F18" s="3">
-        <v>-64500</v>
-      </c>
       <c r="G18" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="H18" s="3">
         <v>-15500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-17200</v>
       </c>
-      <c r="I18" s="3">
-        <v>-10800</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+      <c r="J18" s="3">
+        <v>-10900</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1570,53 +1600,56 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-25900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-24200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-23700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-30000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-28300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-12500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-17700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-10700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,31 +1680,32 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>23400</v>
+        <v>40200</v>
       </c>
       <c r="E20" s="3">
-        <v>-62900</v>
+        <v>-22700</v>
       </c>
       <c r="F20" s="3">
-        <v>-55200</v>
+        <v>63400</v>
       </c>
       <c r="G20" s="3">
-        <v>-26900</v>
+        <v>17000</v>
       </c>
       <c r="H20" s="3">
-        <v>-12400</v>
+        <v>27300</v>
       </c>
       <c r="I20" s="3">
-        <v>700</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>12800</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-500</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1688,27 +1722,27 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
       <c r="T20" s="3">
+        <v>100</v>
+      </c>
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1719,45 +1753,48 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-500</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2900</v>
+        <v>-69900</v>
       </c>
       <c r="E21" s="3">
-        <v>-83900</v>
+        <v>2300</v>
       </c>
       <c r="F21" s="3">
-        <v>-119800</v>
+        <v>-84500</v>
       </c>
       <c r="G21" s="3">
-        <v>-42400</v>
+        <v>-38000</v>
       </c>
       <c r="H21" s="3">
-        <v>-29600</v>
+        <v>-42800</v>
       </c>
       <c r="I21" s="3">
-        <v>-10100</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-30000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-10400</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1819,31 +1856,34 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1905,117 +1945,123 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-68600</v>
+      </c>
+      <c r="E23" s="3">
         <v>2900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-83900</v>
       </c>
-      <c r="F23" s="3">
-        <v>-119800</v>
-      </c>
       <c r="G23" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="H23" s="3">
         <v>-42400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-29600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-19100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-25900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-23100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-27200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-24200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-23700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-29800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-28100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-12400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-17600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2077,8 +2123,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-68600</v>
+      </c>
+      <c r="E26" s="3">
         <v>2900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-83900</v>
       </c>
-      <c r="F26" s="3">
-        <v>-119800</v>
-      </c>
       <c r="G26" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="H26" s="3">
         <v>-42400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-29600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-19100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-23100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-27200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-28400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-24200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-23700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-29800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-28100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-12400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-17600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-68600</v>
+      </c>
+      <c r="E27" s="3">
         <v>2900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-83900</v>
       </c>
-      <c r="F27" s="3">
-        <v>-119800</v>
-      </c>
       <c r="G27" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="H27" s="3">
         <v>-42400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-29600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-19100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-23100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-27200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-28400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-24200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-23700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-29800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-28100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-17600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,31 +2746,34 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-23400</v>
+        <v>-40200</v>
       </c>
       <c r="E32" s="3">
-        <v>62900</v>
+        <v>22700</v>
       </c>
       <c r="F32" s="3">
-        <v>55200</v>
+        <v>-63400</v>
       </c>
       <c r="G32" s="3">
-        <v>26900</v>
+        <v>-17000</v>
       </c>
       <c r="H32" s="3">
-        <v>12400</v>
+        <v>-27300</v>
       </c>
       <c r="I32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>-12800</v>
+      </c>
+      <c r="J32" s="3">
+        <v>500</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -2720,27 +2790,27 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
       <c r="T32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2751,108 +2821,114 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>500</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-68600</v>
+      </c>
+      <c r="E33" s="3">
         <v>2900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-83900</v>
       </c>
-      <c r="F33" s="3">
-        <v>-119800</v>
-      </c>
       <c r="G33" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="H33" s="3">
         <v>-42400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-29600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-19100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-23100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-27200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-28400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-24200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-23700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-29800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-28100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-12400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-17600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-10700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-68600</v>
+      </c>
+      <c r="E35" s="3">
         <v>2900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-83900</v>
       </c>
-      <c r="F35" s="3">
-        <v>-119800</v>
-      </c>
       <c r="G35" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="H35" s="3">
         <v>-42400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-29600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-19100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-23100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-27200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-28400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-24200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-23700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-29800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-28100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-12400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-17600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-10700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,80 +3264,81 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>98900</v>
+      </c>
+      <c r="E41" s="3">
         <v>122200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>146500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>49900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>37500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>35600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>22900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>55700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>38200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>53900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>70200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>78400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>84100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>57500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>48700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>100900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>92500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>18900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>13100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>41100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>14700</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3264,19 +3351,22 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -3288,50 +3378,50 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>13900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>12000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>17400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>26900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>38600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>47200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>64000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>39400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>67800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>37600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>61800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>20000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>19900</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3440,11 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3361,26 +3454,26 @@
       <c r="E43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="F43" s="3">
+        <v>600</v>
+      </c>
+      <c r="G43" s="3">
+        <v>300</v>
+      </c>
+      <c r="H43" s="3">
+        <v>300</v>
+      </c>
+      <c r="I43" s="3">
+        <v>300</v>
+      </c>
+      <c r="J43" s="3">
+        <v>300</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3436,31 +3529,34 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3522,80 +3618,83 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4900</v>
+        <v>3100</v>
       </c>
       <c r="E45" s="3">
-        <v>3900</v>
+        <v>3100</v>
       </c>
       <c r="F45" s="3">
-        <v>4200</v>
+        <v>3600</v>
       </c>
       <c r="G45" s="3">
-        <v>7000</v>
+        <v>3100</v>
       </c>
       <c r="H45" s="3">
-        <v>7200</v>
+        <v>4300</v>
       </c>
       <c r="I45" s="3">
-        <v>6100</v>
+        <v>4500</v>
       </c>
       <c r="J45" s="3">
+        <v>4500</v>
+      </c>
+      <c r="K45" s="3">
         <v>6700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2200</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,80 +3707,83 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>104600</v>
+      </c>
+      <c r="E46" s="3">
         <v>127600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>150900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>54400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>44500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>42800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>29100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>37300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>55500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>76900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>63600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>88400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>116900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>135300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>154400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>102600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>122900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>148500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>163700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>46200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>37000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>46800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16900</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3694,31 +3796,34 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3780,71 +3885,74 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E48" s="3">
         <v>200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1700</v>
-      </c>
-      <c r="S48" s="3">
-        <v>1800</v>
       </c>
       <c r="T48" s="3">
         <v>1800</v>
       </c>
       <c r="U48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="V48" s="3">
         <v>1900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2000</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3857,8 +3965,8 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
@@ -3866,8 +3974,11 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3952,8 +4063,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,8 +4241,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4135,11 +4255,11 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>200</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
@@ -4189,8 +4309,8 @@
       <c r="W52" s="3">
         <v>200</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
+      <c r="X52" s="3">
+        <v>200</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
@@ -4210,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,80 +4419,83 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>106600</v>
+      </c>
+      <c r="E54" s="3">
         <v>127800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>151200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>54800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>45200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>43600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>38400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>56700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>78200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>65000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>89900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>118500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>137000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>156200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>104500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>124800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>150600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>165900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>48400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>37300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>46800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16900</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4382,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,80 +4576,81 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2600</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,31 +4663,34 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4618,80 +4752,83 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>52700</v>
+        <v>83100</v>
       </c>
       <c r="E59" s="3">
-        <v>79900</v>
+        <v>43400</v>
       </c>
       <c r="F59" s="3">
-        <v>69400</v>
+        <v>66800</v>
       </c>
       <c r="G59" s="3">
-        <v>49500</v>
+        <v>54800</v>
       </c>
       <c r="H59" s="3">
-        <v>42500</v>
+        <v>37200</v>
       </c>
       <c r="I59" s="3">
-        <v>27700</v>
+        <v>26500</v>
       </c>
       <c r="J59" s="3">
+        <v>13600</v>
+      </c>
+      <c r="K59" s="3">
         <v>28900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>39500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>43000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>20600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3700</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4704,80 +4841,83 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E60" s="3">
         <v>55400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>83900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>71200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>55500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>47200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>46500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>51700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>30800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>23400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>19800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>20500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>18900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6300</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,13 +4930,16 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -4811,10 +4954,10 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4876,71 +5019,74 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3">
         <v>800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>600</v>
+      </c>
+      <c r="J62" s="3">
+        <v>500</v>
+      </c>
+      <c r="K62" s="3">
+        <v>900</v>
+      </c>
+      <c r="L62" s="3">
+        <v>500</v>
+      </c>
+      <c r="M62" s="3">
+        <v>700</v>
+      </c>
+      <c r="N62" s="3">
         <v>800</v>
       </c>
-      <c r="I62" s="3">
-        <v>800</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="O62" s="3">
         <v>900</v>
       </c>
-      <c r="K62" s="3">
-        <v>500</v>
-      </c>
-      <c r="L62" s="3">
-        <v>700</v>
-      </c>
-      <c r="M62" s="3">
-        <v>800</v>
-      </c>
-      <c r="N62" s="3">
-        <v>900</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1700</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4953,8 +5099,8 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,80 +5375,83 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>100700</v>
+      </c>
+      <c r="E66" s="3">
         <v>55400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>83900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>72000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>56200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>34100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>47100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>31800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>24500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>21000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>22600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>21900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>20400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6300</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5306,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5579,11 +5747,11 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>38500</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,80 +5853,83 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-618200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-549600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-552500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-468600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-430900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-388500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-359000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-348800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-334400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-315300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-289400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-266300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-239200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-210700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-184900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-160700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-137000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-107200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-79100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-66800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-49100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-38400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-30000</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5768,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,80 +6209,83 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E76" s="3">
         <v>72400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>67300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-17100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-11000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-4300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-4100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>42000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>62500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>86700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>112400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>135200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>81900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>102900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>130200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>155800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>32600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>30700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>40000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-27900</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6112,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-68600</v>
+      </c>
+      <c r="E81" s="3">
         <v>2900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-83900</v>
       </c>
-      <c r="F81" s="3">
-        <v>-119800</v>
-      </c>
       <c r="G81" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="H81" s="3">
         <v>-42400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-29600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-19100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-23100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-27200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-28400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-24200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-23700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-29800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-28100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-12400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-17600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-10700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,31 +6605,32 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -6439,8 +6638,8 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -6448,8 +6647,8 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -6493,8 +6692,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-22600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-18900</v>
       </c>
-      <c r="F89" s="3">
-        <v>-55200</v>
-      </c>
       <c r="G89" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="H89" s="3">
         <v>-14700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-16500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-15900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-18400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-24400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-26900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-25900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-22200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-22800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-20700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-15900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-18900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-12400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,31 +7261,32 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -7127,8 +7348,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,71 +7526,74 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>13900</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>13900</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>5000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>5500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>9500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>11800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>8500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>16800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-24700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>28400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-30200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>24000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-41700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7376,8 +7606,8 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -7385,8 +7615,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,31 +7650,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,117 +8004,123 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>115500</v>
       </c>
-      <c r="F100" s="3">
-        <v>74500</v>
-      </c>
       <c r="G100" s="3">
+        <v>29400</v>
+      </c>
+      <c r="H100" s="3">
         <v>16600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>29200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>30400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>73500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>134200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>18300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>35400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2900</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>5600</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7933,90 +8182,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-24300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>96600</v>
       </c>
-      <c r="F102" s="3">
-        <v>33200</v>
-      </c>
       <c r="G102" s="3">
+        <v>12400</v>
+      </c>
+      <c r="H102" s="3">
         <v>1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-23700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>17500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>26600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-52200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>73700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-28000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>26400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4400</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/APLT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APLT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
   <si>
     <t>APLT</t>
   </si>
@@ -656,166 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>10700</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -828,11 +835,11 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -873,38 +880,44 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F9" s="3">
         <v>14800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>10000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>12200</v>
       </c>
-      <c r="G9" s="3">
-        <v>53900</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>15300</v>
+      </c>
+      <c r="J9" s="3">
         <v>10800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>11900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>15900</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -962,38 +975,44 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="F10" s="3">
         <v>-14700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-9900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-12000</v>
       </c>
-      <c r="G10" s="3">
-        <v>-54600</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="J10" s="3">
         <v>-10800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-11900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-5300</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1051,8 +1070,14 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,97 +1109,105 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F12" s="3">
         <v>14800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>10000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>12200</v>
       </c>
-      <c r="G12" s="3">
-        <v>-38600</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
+        <v>15300</v>
+      </c>
+      <c r="J12" s="3">
         <v>10800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>11900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>15900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>12100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>13100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>15400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>15000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>15700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>17600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>14800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>14400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>13800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>19900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>20800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>7300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>13800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>7500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>4300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>6900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>1400</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,37 +1295,43 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1351,8 +1390,14 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1485,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,127 +1521,135 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F17" s="3">
         <v>29900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>20600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>21300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>20300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>15500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>17200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>21500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>19000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>19400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>21500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>23100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>27100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>28400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>25900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>24200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>23700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>30000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>28300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>12500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>17700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>10700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>8400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>8700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1900</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-29700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-20400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-21100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-21000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-15500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-17200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-10900</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1603,53 +1662,59 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>-25900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-24200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-23700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-30000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-28300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-12500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-17700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,38 +1746,40 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-76100</v>
+      </c>
+      <c r="F20" s="3">
         <v>40200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-22700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>63400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>17000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>27300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>12800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1725,29 +1792,29 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>100</v>
-      </c>
-      <c r="U20" s="3">
-        <v>200</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
       </c>
       <c r="W20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
@@ -1756,52 +1823,58 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-500</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>43000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-69900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-84500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-38000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-42800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-30000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-10400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1859,8 +1932,14 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1885,11 +1964,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1948,97 +2027,109 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-68600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-83900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-37700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-42400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-29600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-10100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-14400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-19100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-25900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-23100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-27200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-25800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-24200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-23700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-29800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-28100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-12400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-17600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2063,11 +2154,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2126,8 +2217,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2312,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-68600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>2900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-83900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-37700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-42400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-29600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-10100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-14400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-19100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-25900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-23100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-27200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-25800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-24200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-23700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-29800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-28100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-12400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-17600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-68600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>2900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-83900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-37700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-42400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-29600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-10100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-14400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-19100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-25900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-23100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-27200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-25800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-24200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-23700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-29800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-28100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-12400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-17600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2597,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2692,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2787,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,38 +2882,44 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>76100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-40200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>22700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-63400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-17000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-27300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-12800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,29 +2932,29 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-200</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
       </c>
       <c r="W32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="X32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
@@ -2824,111 +2963,123 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>500</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-68600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>2900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-83900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-37700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-42400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-29600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-10100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-14400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-19100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-25900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-23100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-27200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-25800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-24200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-23700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-29800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-28100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-12400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-17600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3167,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-68600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>2900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-83900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-37700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-42400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-29600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-10100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-14400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-19100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-25900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-23100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-27200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-25800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-24200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-23700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-29800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-28100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-12400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-17600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3401,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,86 +3436,88 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>79400</v>
+      </c>
+      <c r="F41" s="3">
         <v>98900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>122200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>146500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>49900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>37500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>35600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>22900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>16700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>40400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>55700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>38200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>53900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>70200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>78400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>84100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>57500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>48700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>100900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>92500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>18900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>13100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>41100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>14700</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3354,8 +3527,14 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3381,53 +3560,53 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>13900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>7000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>12000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>17400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>26900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>38600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>47200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>64000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>39400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>67800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>37600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>61800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>20000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>19900</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3443,43 +3622,49 @@
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>300</v>
-      </c>
-      <c r="E43" s="3">
-        <v>300</v>
-      </c>
-      <c r="F43" s="3">
-        <v>600</v>
       </c>
       <c r="G43" s="3">
         <v>300</v>
       </c>
       <c r="H43" s="3">
-        <v>300</v>
-      </c>
-      <c r="I43" s="3">
-        <v>300</v>
+        <v>600</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="K43" s="3">
+        <v>300</v>
+      </c>
+      <c r="L43" s="3">
+        <v>300</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -3532,8 +3717,14 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3558,11 +3749,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3621,86 +3812,92 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F45" s="3">
         <v>3100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3600</v>
       </c>
       <c r="G45" s="3">
         <v>3100</v>
       </c>
       <c r="H45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J45" s="3">
         <v>4300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>4500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>4500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>6700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>8100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>9200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>7900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>7600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>8100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>9600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>6300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>5800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>6400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>10000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>9400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>7300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>4100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>5700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>2200</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3710,86 +3907,92 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>83600</v>
+      </c>
+      <c r="F46" s="3">
         <v>104600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>127600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>150900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>54400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>44500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>42800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>29100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>37300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>55500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>76900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>63600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>88400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>116900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>135300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>154400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>102600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>122900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>148500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>163700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>46200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>37000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>46800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>16900</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3799,8 +4002,14 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3825,11 +4034,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3888,77 +4097,83 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F48" s="3">
         <v>2000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2000</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3968,17 +4183,23 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>0</v>
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4287,14 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4382,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,16 +4477,22 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>300</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -4261,11 +4500,11 @@
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H52" s="3">
-        <v>200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>200</v>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3">
         <v>200</v>
@@ -4312,11 +4551,11 @@
       <c r="X52" s="3">
         <v>200</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
+      <c r="Y52" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>200</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
@@ -4333,8 +4572,14 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,86 +4667,92 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>86700</v>
+      </c>
+      <c r="F54" s="3">
         <v>106600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>127800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>151200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>54800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>45200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>43600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>30000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>38400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>56700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>78200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>65000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>89900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>118500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>137000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>156200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>104500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>124800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>150600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>165900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>48400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>37300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>46800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>16900</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4511,8 +4762,14 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4801,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,86 +4836,88 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F57" s="3">
         <v>2800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>4700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>5600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>4500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>7000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>8700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>5900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>9500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>9200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>3300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>3500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>5600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>8800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>4000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>2600</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4666,38 +4927,44 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E58" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F58" s="3">
         <v>300</v>
       </c>
       <c r="G58" s="3">
+        <v>200</v>
+      </c>
+      <c r="H58" s="3">
+        <v>300</v>
+      </c>
+      <c r="I58" s="3">
         <v>700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4755,86 +5022,92 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F59" s="3">
         <v>83100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>43400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>66800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>54800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>37200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>26500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>13600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>28900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>39500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>43000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>16300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>17000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>21700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>20100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>16300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>20600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>18600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>13200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>6900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>5300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>4800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>3700</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4844,86 +5117,92 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>27300</v>
+      </c>
+      <c r="F60" s="3">
         <v>99000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>55400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>83900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>71200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>55500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>47200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>33300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>33400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>46500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>51700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>22200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>26500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>30800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>23400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>19800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>21200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>20500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>18900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>8500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>14100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>6500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>6800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>6300</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4933,20 +5212,26 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F61" s="3">
         <v>1700</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -4954,17 +5239,17 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5022,8 +5307,14 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5036,63 +5327,63 @@
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
         <v>800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>600</v>
-      </c>
-      <c r="J62" s="3">
-        <v>500</v>
-      </c>
-      <c r="K62" s="3">
-        <v>900</v>
       </c>
       <c r="L62" s="3">
         <v>500</v>
       </c>
       <c r="M62" s="3">
+        <v>900</v>
+      </c>
+      <c r="N62" s="3">
+        <v>500</v>
+      </c>
+      <c r="O62" s="3">
         <v>700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1700</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5102,17 +5393,23 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5497,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5592,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,86 +5687,92 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F66" s="3">
         <v>100700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>55400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>83900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>72000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>56200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>48000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>34100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>34300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>47100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>52400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>23000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>27400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>31800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>24500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>21000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>22600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>21900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>20400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>10100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>15800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>6500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>6800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>6300</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,8 +5782,14 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5821,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5912,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6007,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5750,14 +6085,14 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>38500</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
@@ -5767,8 +6102,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,86 +6197,92 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-596000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-574200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-618200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-549600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-552500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-468600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-430900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-388500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-359000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-348800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-334400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-315300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-289400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-266300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-239200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-210700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-184900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-160700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-137000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-107200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-79100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-66800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-49100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-38400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-30000</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5945,8 +6292,14 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6387,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6482,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,86 +6577,92 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>57000</v>
+      </c>
+      <c r="F76" s="3">
         <v>5900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>72400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>67300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-17100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-11000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-4300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-4100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>9600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>25800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>42000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>62500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>86700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>112400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>135200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>81900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>102900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>130200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>155800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>32600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>30700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>40000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-27900</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6301,8 +6672,14 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6767,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-68600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>2900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-83900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-37700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-42400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-29600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-10100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-14400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-19100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-25900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-23100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-27200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-25800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-24200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-23700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-29800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-28100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-12400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-17600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +7001,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6615,7 +7012,7 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -6633,28 +7030,28 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -6695,8 +7092,14 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7187,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7282,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7377,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7472,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7567,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-23300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-22600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-18900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-17000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-14700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-16500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-7000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-15900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-19400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-18400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-24400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-26900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-25900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-22200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-22800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-20700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-15900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-18900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-12400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7701,10 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7288,11 +7729,11 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -7351,8 +7792,14 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7887,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7982,14 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7543,63 +8002,63 @@
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>13900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-6900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>5000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>5500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>9500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>11800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>8500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>16800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-24700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>28400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-30200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>24000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-41700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7609,17 +8068,23 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +8116,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7677,11 +8144,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7740,8 +8207,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8302,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8397,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,97 +8492,109 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-1700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>115500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>29400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>16600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>29200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>30400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>3500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>73500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>3100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>134200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>18300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>35400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>2900</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>5600</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8122,11 +8619,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8185,93 +8682,105 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-23300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-24300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>96600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>12400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>12700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>6300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-23700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-15300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>17500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-15700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-16300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-5600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>26600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>8800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-52200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>8400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>73700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>5800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>26400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>4400</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/APLT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/APLT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="92">
   <si>
     <t>APLT</t>
   </si>
@@ -656,176 +656,180 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3">
         <v>100</v>
       </c>
       <c r="H8" s="3">
+        <v>100</v>
+      </c>
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3">
         <v>10700</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -841,8 +845,8 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -886,41 +890,44 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E9" s="3">
         <v>7800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15900</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -981,41 +988,44 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E10" s="3">
         <v>-7800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-11700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-14700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-9900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-12000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-16000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-10800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-11900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-5300</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1076,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,103 +1124,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E12" s="3">
         <v>7800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>15300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>11900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>17600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>14800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>14400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>19900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>20800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>13800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>4300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>6900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1400</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,16 +1318,19 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1321,20 +1341,20 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,136 +1549,140 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E17" s="3">
         <v>25500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>33000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>20600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>19400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>28400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>25900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>24200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>23700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>30000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>28300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>17700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1900</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-25500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-33000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-29700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-20400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-21100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-21000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-15500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-17200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10900</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1668,53 +1698,56 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>-25900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-24200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-23700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-30000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-28300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-12500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-17700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,41 +1781,42 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-76100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>40200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-22700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>63400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>17000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>27300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1798,27 +1832,27 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
       </c>
       <c r="W20" s="3">
+        <v>100</v>
+      </c>
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1829,55 +1863,58 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-500</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-22400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>43000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-69900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-84500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-38000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-42800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-30000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1938,8 +1975,11 @@
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1970,8 +2010,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2033,103 +2073,109 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>44000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-68600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-83900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-37700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-42400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-29600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-25900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-23100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-27200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-28400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-25800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-24200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-23700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-29800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-28100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-17600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2160,8 +2206,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2223,8 +2269,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-21800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>44000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-68600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-83900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-37700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-42400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-29600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-19100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-25900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-23100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-27200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-28400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-25800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-24200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-23700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-29800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-28100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-17600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>44000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-68600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-83900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-37700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-42400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-29600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-25900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-23100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-27200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-28400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-25800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-24200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-23700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-29800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-28100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-17600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,41 +2955,44 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>3100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>76100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-40200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>22700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-63400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-17000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-27300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2938,27 +3008,27 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
       <c r="U32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
       </c>
       <c r="W32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -2969,117 +3039,123 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>500</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-21800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>44000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-68600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-83900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-37700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-42400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-29600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-25900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-23100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-27200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-28400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-25800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-24200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-23700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-29800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-28100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-17600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-21800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>44000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-68600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-83900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-37700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-42400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-29600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-25900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-23100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-27200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-28400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-25800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-24200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-23700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-29800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-28100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-17600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,89 +3524,90 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E41" s="3">
         <v>50800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>79400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>98900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>122200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>146500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>49900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>37500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>35600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>22900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>40400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>55700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>38200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>53900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>70200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>78400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>84100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>57500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>48700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>100900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>92500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>18900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>41100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>14700</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,8 +3620,11 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3566,50 +3656,50 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>13900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>12000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>17400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>26900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>38600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>47200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>64000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>39400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>67800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>37600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>61800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>20000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>19900</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3628,8 +3718,11 @@
       <c r="AG42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3639,20 +3732,20 @@
       <c r="E43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F43" s="3">
-        <v>300</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G43" s="3">
         <v>300</v>
       </c>
       <c r="H43" s="3">
+        <v>300</v>
+      </c>
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3">
-        <v>300</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>300</v>
@@ -3660,14 +3753,14 @@
       <c r="L43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
+      <c r="M43" s="3">
+        <v>300</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -3723,8 +3816,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3755,8 +3851,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3818,89 +3914,92 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E45" s="3">
         <v>1900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3100</v>
       </c>
       <c r="G45" s="3">
         <v>3100</v>
       </c>
       <c r="H45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I45" s="3">
         <v>3600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4300</v>
-      </c>
-      <c r="K45" s="3">
-        <v>4500</v>
       </c>
       <c r="L45" s="3">
         <v>4500</v>
       </c>
       <c r="M45" s="3">
+        <v>4500</v>
+      </c>
+      <c r="N45" s="3">
         <v>6700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>9400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2200</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3913,89 +4012,92 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E46" s="3">
         <v>54000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>83600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>104600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>127600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>150900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>54400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>44500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>42800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>29100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>37300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>55500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>76900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>63600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>88400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>116900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>135300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>154400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>102600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>122900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>148500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>163700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>46200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>37000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>46800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16900</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4008,8 +4110,11 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4040,8 +4145,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4103,80 +4208,83 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E48" s="3">
         <v>2700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1700</v>
-      </c>
-      <c r="V48" s="3">
-        <v>1800</v>
       </c>
       <c r="W48" s="3">
         <v>1800</v>
       </c>
       <c r="X48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Y48" s="3">
         <v>1900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4189,8 +4297,8 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE48" s="3">
-        <v>0</v>
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF48" s="3">
         <v>0</v>
@@ -4198,8 +4306,11 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4293,8 +4404,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,8 +4600,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4494,8 +4614,8 @@
       <c r="E52" s="3">
         <v>300</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+      <c r="F52" s="3">
+        <v>300</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
@@ -4506,8 +4626,8 @@
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J52" s="3">
-        <v>200</v>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>200</v>
@@ -4557,8 +4677,8 @@
       <c r="Z52" s="3">
         <v>200</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
+      <c r="AA52" s="3">
+        <v>200</v>
       </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
@@ -4578,8 +4698,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,89 +4796,92 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E54" s="3">
         <v>56900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>86700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>106600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>127800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>151200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>54800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>45200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>30000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>38400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>56700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>78200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>65000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>89900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>118500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>137000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>156200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>104500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>124800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>150600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>165900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>48400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>37300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>46800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>16900</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4768,8 +4894,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4847,80 +4978,80 @@
         <v>4900</v>
       </c>
       <c r="E57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F57" s="3">
         <v>4400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>8800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2600</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4933,8 +5064,11 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4945,29 +5079,29 @@
         <v>400</v>
       </c>
       <c r="F58" s="3">
+        <v>400</v>
+      </c>
+      <c r="G58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>500</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5028,89 +5162,92 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E59" s="3">
         <v>3900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>83100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>43400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>66800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>54800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>37200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>26500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>39500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>43000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>20100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>20600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3700</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5123,89 +5260,92 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E60" s="3">
         <v>18000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>99000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>55400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>83900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>71200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>55500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>47200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>46500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>51700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>26500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>30800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>23400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>19800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>20500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>18900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6300</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5218,23 +5358,26 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1700</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -5245,14 +5388,14 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5313,8 +5456,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5333,60 +5479,60 @@
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1700</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5399,8 +5545,8 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,89 +5848,92 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E66" s="3">
         <v>20200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>29700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>100700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>55400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>83900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>72000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>56200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>48000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>34100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>34300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>47100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>52400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>27400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>31800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>24500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>21000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>22600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>21900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>20400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6300</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5788,8 +5946,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6091,11 +6259,11 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
         <v>38500</v>
       </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,89 +6374,92 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-617400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-596000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-574200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-618200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-549600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-552500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-468600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-430900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-388500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-359000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-348800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-334400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-315300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-289400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-266300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-239200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-210700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-184900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-160700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-137000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-107200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-79100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-66800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-49100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-38400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-30000</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6298,8 +6472,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,89 +6766,92 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E76" s="3">
         <v>36700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>57000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>72400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>67300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-17100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-11000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-4300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-4100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>25800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>42000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>62500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>86700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>112400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>135200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>81900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>102900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>130200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>155800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>32600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>30700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>40000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-27900</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6678,8 +6864,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-21800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>44000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-68600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-83900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-37700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-42400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-29600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-25900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-23100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-27200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-28400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-25800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-24200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-23700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-29800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-28100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-17600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7012,10 +7211,10 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -7036,7 +7235,7 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -7044,8 +7243,8 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -7053,8 +7252,8 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -7098,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-28600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-19500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-23300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-22600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-18900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-17000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-16500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-19400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-18400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-26900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-25900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-22200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-22800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-20700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-15900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-18900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-12400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-9100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7735,8 +7956,8 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -7798,8 +8019,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,8 +8215,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8008,8 +8238,8 @@
       <c r="H94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
@@ -8018,50 +8248,50 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>13900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>5000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>5500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>9500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>11800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>8500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>16800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-24700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>28400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-30200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>24000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-41700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8074,8 +8304,8 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF94" s="3">
         <v>0</v>
@@ -8083,8 +8313,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8150,8 +8384,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,103 +8741,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-1700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>115500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>29400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>16600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>29200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>30400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>73500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>134200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>18300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>35400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2900</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>5600</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8625,8 +8874,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8688,99 +8937,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-28600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-19500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-23300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-24300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>96600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>12700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-23700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-15300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-16300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>26600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-52200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>8400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>73700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>26400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>4400</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
